--- a/web-reports/latest/Excel/Execution_Summary.xlsx
+++ b/web-reports/latest/Excel/Execution_Summary.xlsx
@@ -40,7 +40,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>0.04s</t>
+    <t>0.05s</t>
   </si>
 </sst>
 </file>

--- a/web-reports/latest/Excel/Execution_Summary.xlsx
+++ b/web-reports/latest/Excel/Execution_Summary.xlsx
@@ -40,7 +40,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>0.05s</t>
+    <t>0.04s</t>
   </si>
 </sst>
 </file>
